--- a/datos/fab_queso_bm_limpio.xlsx
+++ b/datos/fab_queso_bm_limpio.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{B8CF4EC8-E41A-4C36-8338-D8563CC685A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9656F89B-8F3D-4183-8FF8-CE4404BC102E}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{B8CF4EC8-E41A-4C36-8338-D8563CC685A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B5F8B1F-6EE6-4925-9C44-414895727822}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{7FECADBA-BDAD-4006-8F58-8A23F77455D6}"/>
   </bookViews>
   <sheets>
     <sheet name="fab_queso_bm_limpio" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">fab_queso_bm_limpio!$A$1:$O$46</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -67,9 +70,6 @@
     <t>sal_queso</t>
   </si>
   <si>
-    <t>light</t>
-  </si>
-  <si>
     <t>3 kg</t>
   </si>
   <si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>oveja dop</t>
+  </si>
+  <si>
+    <t>bajo en grasa</t>
   </si>
 </sst>
 </file>
@@ -634,6 +637,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -955,6 +962,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B95C387-324B-4031-B14C-3CFF05230B84}">
   <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1008,7 +1018,7 @@
         <v>44615</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>12330</v>
@@ -1032,7 +1042,7 @@
         <v>6.46</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K2">
         <v>50.85</v>
@@ -1055,7 +1065,7 @@
         <v>44616</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>7500</v>
@@ -1079,7 +1089,7 @@
         <v>6.35</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K3">
         <v>57.42</v>
@@ -1102,7 +1112,7 @@
         <v>44621</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>13030</v>
@@ -1126,7 +1136,7 @@
         <v>6.4</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K4">
         <v>53.32</v>
@@ -1149,7 +1159,7 @@
         <v>44621</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5">
         <v>14820</v>
@@ -1173,7 +1183,7 @@
         <v>6.38</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K5">
         <v>56.94</v>
@@ -1196,7 +1206,7 @@
         <v>44624</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>11890</v>
@@ -1220,7 +1230,7 @@
         <v>6.42</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N6">
         <v>2051</v>
@@ -1231,7 +1241,7 @@
         <v>44624</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>14020</v>
@@ -1255,7 +1265,7 @@
         <v>6.41</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K7">
         <v>55.18</v>
@@ -1278,7 +1288,7 @@
         <v>44624</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>13530</v>
@@ -1302,7 +1312,7 @@
         <v>6.31</v>
       </c>
       <c r="J8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K8">
         <v>57.22</v>
@@ -1325,7 +1335,7 @@
         <v>44628</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C9">
         <v>10660</v>
@@ -1349,7 +1359,7 @@
         <v>6.47</v>
       </c>
       <c r="J9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K9">
         <v>50.26</v>
@@ -1372,7 +1382,7 @@
         <v>44628</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>13750</v>
@@ -1396,7 +1406,7 @@
         <v>6.4</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K10">
         <v>59.78</v>
@@ -1419,7 +1429,7 @@
         <v>44630</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>9490</v>
@@ -1443,7 +1453,7 @@
         <v>6.36</v>
       </c>
       <c r="J11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K11">
         <v>54.97</v>
@@ -1466,7 +1476,7 @@
         <v>44631</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12">
         <v>12030</v>
@@ -1490,7 +1500,7 @@
         <v>6.35</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K12">
         <v>57.99</v>
@@ -1513,7 +1523,7 @@
         <v>44635</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13">
         <v>15030</v>
@@ -1534,7 +1544,7 @@
         <v>4.3</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K13">
         <v>57.81</v>
@@ -1557,7 +1567,7 @@
         <v>44635</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14">
         <v>13830</v>
@@ -1581,7 +1591,7 @@
         <v>6.46</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K14">
         <v>58.02</v>
@@ -1604,7 +1614,7 @@
         <v>44637</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15">
         <v>9520</v>
@@ -1628,7 +1638,7 @@
         <v>6.24</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K15">
         <v>56.87</v>
@@ -1651,7 +1661,7 @@
         <v>44638</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16">
         <v>14530</v>
@@ -1675,7 +1685,7 @@
         <v>6.42</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N16">
         <v>2250</v>
@@ -1686,7 +1696,7 @@
         <v>44645</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17">
         <v>13230</v>
@@ -1710,7 +1720,7 @@
         <v>6.42</v>
       </c>
       <c r="J17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K17">
         <v>57.1</v>
@@ -1733,7 +1743,7 @@
         <v>44649</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <v>12630</v>
@@ -1757,7 +1767,7 @@
         <v>6.42</v>
       </c>
       <c r="J18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L18">
         <v>20.100000000000001</v>
@@ -1777,7 +1787,7 @@
         <v>44652</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19">
         <v>15340</v>
@@ -1801,7 +1811,7 @@
         <v>6.48</v>
       </c>
       <c r="J19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K19">
         <v>59.02</v>
@@ -1824,7 +1834,7 @@
         <v>44656</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C20">
         <v>14530</v>
@@ -1845,7 +1855,7 @@
         <v>4.53</v>
       </c>
       <c r="J20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K20">
         <v>52.04</v>
@@ -1868,7 +1878,7 @@
         <v>44659</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21">
         <v>10850</v>
@@ -1892,7 +1902,7 @@
         <v>6.42</v>
       </c>
       <c r="J21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K21">
         <v>57.45</v>
@@ -1915,7 +1925,7 @@
         <v>44659</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22">
         <v>15830</v>
@@ -1939,7 +1949,7 @@
         <v>6.41</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K22">
         <v>56.63</v>
@@ -1962,7 +1972,7 @@
         <v>44663</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C23">
         <v>14530</v>
@@ -1983,7 +1993,7 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="J23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K23">
         <v>52.48</v>
@@ -2006,7 +2016,7 @@
         <v>44664</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C24">
         <v>9020</v>
@@ -2030,7 +2040,7 @@
         <v>6.39</v>
       </c>
       <c r="J24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K24">
         <v>55.37</v>
@@ -2053,7 +2063,7 @@
         <v>44666</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C25">
         <v>14050</v>
@@ -2077,7 +2087,7 @@
         <v>6.4</v>
       </c>
       <c r="J25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K25">
         <v>58.68</v>
@@ -2100,7 +2110,7 @@
         <v>44670</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26">
         <v>11940</v>
@@ -2124,7 +2134,7 @@
         <v>6.39</v>
       </c>
       <c r="J26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K26">
         <v>58.34</v>
@@ -2147,7 +2157,7 @@
         <v>44670</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C27">
         <v>12780</v>
@@ -2168,7 +2178,7 @@
         <v>3.9</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K27">
         <v>52.14</v>
@@ -2191,7 +2201,7 @@
         <v>44673</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28">
         <v>13910</v>
@@ -2212,7 +2222,7 @@
         <v>3.86</v>
       </c>
       <c r="J28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K28">
         <v>55.13</v>
@@ -2235,7 +2245,7 @@
         <v>44680</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C29">
         <v>15350</v>
@@ -2259,7 +2269,7 @@
         <v>6.4</v>
       </c>
       <c r="J29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K29">
         <v>50.48</v>
@@ -2282,7 +2292,7 @@
         <v>44680</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C30">
         <v>15440</v>
@@ -2303,7 +2313,7 @@
         <v>4.3099999999999996</v>
       </c>
       <c r="J30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K30">
         <v>57.45</v>
@@ -2326,7 +2336,7 @@
         <v>44684</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C31">
         <v>13790</v>
@@ -2350,7 +2360,7 @@
         <v>6.39</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K31">
         <v>57.77</v>
@@ -2373,7 +2383,7 @@
         <v>44687</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C32">
         <v>15130</v>
@@ -2397,7 +2407,7 @@
         <v>6.39</v>
       </c>
       <c r="J32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K32">
         <v>50.26</v>
@@ -2420,7 +2430,7 @@
         <v>44687</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C33">
         <v>11780</v>
@@ -2444,7 +2454,7 @@
         <v>6.43</v>
       </c>
       <c r="J33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K33">
         <v>56.12</v>
@@ -2467,7 +2477,7 @@
         <v>44691</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C34">
         <v>13910</v>
@@ -2491,7 +2501,7 @@
         <v>6.4</v>
       </c>
       <c r="J34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K34">
         <v>56.72</v>
@@ -2514,7 +2524,7 @@
         <v>44691</v>
       </c>
       <c r="B35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C35">
         <v>14840</v>
@@ -2538,7 +2548,7 @@
         <v>6.4</v>
       </c>
       <c r="J35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K35">
         <v>56.95</v>
@@ -2561,7 +2571,7 @@
         <v>44694</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C36">
         <v>13390</v>
@@ -2585,7 +2595,7 @@
         <v>6.41</v>
       </c>
       <c r="J36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K36">
         <v>56.85</v>
@@ -2608,7 +2618,7 @@
         <v>44698</v>
       </c>
       <c r="B37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C37">
         <v>12530</v>
@@ -2632,7 +2642,7 @@
         <v>6.41</v>
       </c>
       <c r="J37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K37">
         <v>56.74</v>
@@ -2655,7 +2665,7 @@
         <v>44698</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C38">
         <v>11130</v>
@@ -2679,7 +2689,7 @@
         <v>6.43</v>
       </c>
       <c r="J38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K38">
         <v>57.95</v>
@@ -2702,7 +2712,7 @@
         <v>44701</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C39">
         <v>11030</v>
@@ -2726,7 +2736,7 @@
         <v>6.42</v>
       </c>
       <c r="J39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K39">
         <v>58.44</v>
@@ -2749,7 +2759,7 @@
         <v>44701</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40">
         <v>14090</v>
@@ -2773,7 +2783,7 @@
         <v>6.34</v>
       </c>
       <c r="J40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K40">
         <v>58.39</v>
@@ -2796,7 +2806,7 @@
         <v>44701</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C41">
         <v>11450</v>
@@ -2820,7 +2830,7 @@
         <v>6.38</v>
       </c>
       <c r="J41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K41">
         <v>57.25</v>
@@ -2843,7 +2853,7 @@
         <v>44705</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C42">
         <v>13030</v>
@@ -2867,7 +2877,7 @@
         <v>6.4</v>
       </c>
       <c r="J42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K42">
         <v>56.76</v>
@@ -2890,7 +2900,7 @@
         <v>44706</v>
       </c>
       <c r="B43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C43">
         <v>9910</v>
@@ -2914,7 +2924,7 @@
         <v>6.38</v>
       </c>
       <c r="J43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K43">
         <v>54.4</v>
@@ -2937,7 +2947,7 @@
         <v>44706</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C44">
         <v>12320</v>
@@ -2958,7 +2968,7 @@
         <v>4.16</v>
       </c>
       <c r="J44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K44">
         <v>52.67</v>
@@ -2981,7 +2991,7 @@
         <v>44708</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C45">
         <v>11680</v>
@@ -3005,7 +3015,7 @@
         <v>6.44</v>
       </c>
       <c r="J45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K45">
         <v>58.99</v>
@@ -3028,7 +3038,7 @@
         <v>44711</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C46">
         <v>12080</v>
@@ -3052,7 +3062,7 @@
         <v>6.36</v>
       </c>
       <c r="J46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K46">
         <v>57.14</v>
@@ -3071,6 +3081,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O46" xr:uid="{5B95C387-324B-4031-B14C-3CFF05230B84}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>